--- a/backend/data/financials_by_company/123.F.xlsx
+++ b/backend/data/financials_by_company/123.F.xlsx
@@ -662,136 +662,132 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-150326.687647</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.012624</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-1766644</v>
+        <v>-3543544</v>
       </c>
       <c r="E2" t="n">
-        <v>-11908245</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-11908245</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-7089318</v>
+        <v>-3142609</v>
       </c>
       <c r="H2" t="n">
-        <v>-13674889</v>
+        <v>-3543544</v>
       </c>
       <c r="I2" t="n">
-        <v>-13674889</v>
+        <v>-3543544</v>
       </c>
       <c r="J2" t="n">
-        <v>11479</v>
-      </c>
-      <c r="K2" t="n">
-        <v>29440</v>
-      </c>
+        <v>3971</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>40919</v>
+        <v>3971</v>
       </c>
       <c r="M2" t="n">
-        <v>4668600.312353</v>
+        <v>-3142609</v>
       </c>
       <c r="N2" t="n">
-        <v>-7089318</v>
+        <v>-3142609</v>
       </c>
       <c r="O2" t="n">
-        <v>1908481</v>
+        <v>3543544</v>
       </c>
       <c r="P2" t="n">
-        <v>3047805</v>
+        <v>7280550</v>
       </c>
       <c r="Q2" t="n">
-        <v>3047805</v>
+        <v>7280550</v>
       </c>
       <c r="R2" t="n">
-        <v>-2.35</v>
+        <v>-0.45</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.35</v>
+        <v>-0.45</v>
       </c>
       <c r="T2" t="n">
-        <v>-7089318</v>
+        <v>-3142609</v>
       </c>
       <c r="U2" t="n">
-        <v>-7089318</v>
+        <v>-3142609</v>
       </c>
       <c r="V2" t="n">
-        <v>-7089318</v>
+        <v>-3142609</v>
       </c>
       <c r="W2" t="n">
-        <v>6442011</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-13531329</v>
+        <v>-3142609</v>
       </c>
       <c r="Y2" t="n">
-        <v>-13531329</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-173000</v>
-      </c>
+        <v>-3142609</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>-13704329</v>
+        <v>-3142609</v>
       </c>
       <c r="AB2" t="n">
-        <v>-11807327</v>
+        <v>396964</v>
       </c>
       <c r="AC2" t="n">
-        <v>100918</v>
+        <v>396964</v>
       </c>
       <c r="AD2" t="n">
-        <v>-10861288</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>10861288</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1046957</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>11479</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>29440</v>
-      </c>
+        <v>3971</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>40919</v>
+        <v>3971</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1908481</v>
+        <v>-3543544</v>
       </c>
       <c r="AN2" t="n">
-        <v>1908481</v>
+        <v>3543544</v>
       </c>
       <c r="AO2" t="n">
-        <v>436388</v>
+        <v>310078</v>
       </c>
       <c r="AP2" t="n">
-        <v>1472093</v>
+        <v>3233466</v>
       </c>
       <c r="AQ2" t="n">
-        <v>568489</v>
+        <v>730159</v>
       </c>
       <c r="AR2" t="n">
-        <v>903604</v>
+        <v>2503307</v>
       </c>
       <c r="AS2" t="n">
-        <v>700562</v>
+        <v>857113</v>
       </c>
       <c r="AT2" t="n">
-        <v>203042</v>
+        <v>1646194</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -802,140 +798,136 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-296385.2</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-2992593</v>
+        <v>-5684172</v>
       </c>
       <c r="E3" t="n">
-        <v>-740963</v>
+        <v>2981509</v>
       </c>
       <c r="F3" t="n">
-        <v>-740963</v>
+        <v>2981509</v>
       </c>
       <c r="G3" t="n">
-        <v>-3058383</v>
+        <v>670714</v>
       </c>
       <c r="H3" t="n">
-        <v>-3733556</v>
+        <v>-2702663</v>
       </c>
       <c r="I3" t="n">
-        <v>-3733556</v>
+        <v>-2702663</v>
       </c>
       <c r="J3" t="n">
-        <v>82450</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+        <v>11865</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>82450</v>
+        <v>11865</v>
       </c>
       <c r="M3" t="n">
-        <v>-2613805.2</v>
+        <v>-2310795</v>
       </c>
       <c r="N3" t="n">
-        <v>-3058383</v>
+        <v>670714</v>
       </c>
       <c r="O3" t="n">
-        <v>3495589</v>
+        <v>2702663</v>
       </c>
       <c r="P3" t="n">
-        <v>2967566</v>
+        <v>9972243</v>
       </c>
       <c r="Q3" t="n">
-        <v>2967566</v>
+        <v>9972243</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.05</v>
+        <v>0.05</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.05</v>
+        <v>0.05</v>
       </c>
       <c r="T3" t="n">
-        <v>-3058383</v>
+        <v>670714</v>
       </c>
       <c r="U3" t="n">
-        <v>-3058383</v>
+        <v>670714</v>
       </c>
       <c r="V3" t="n">
-        <v>-3058383</v>
+        <v>670714</v>
       </c>
       <c r="W3" t="n">
-        <v>848173</v>
+        <v>270977</v>
       </c>
       <c r="X3" t="n">
-        <v>-3906556</v>
+        <v>399737</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3906556</v>
+        <v>399737</v>
       </c>
       <c r="Z3" t="n">
-        <v>173000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3733556</v>
+        <v>399737</v>
       </c>
       <c r="AB3" t="n">
-        <v>-320417</v>
+        <v>3090535</v>
       </c>
       <c r="AC3" t="n">
-        <v>420546</v>
+        <v>109026</v>
       </c>
       <c r="AD3" t="n">
-        <v>-433311</v>
+        <v>1059643</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1401043</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-341400</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>433311</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-307652</v>
+        <v>1921866</v>
       </c>
       <c r="AJ3" t="n">
-        <v>82450</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
+        <v>11865</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>82450</v>
+        <v>11865</v>
       </c>
       <c r="AM3" t="n">
-        <v>-3495589</v>
+        <v>-2702663</v>
       </c>
       <c r="AN3" t="n">
-        <v>3495589</v>
+        <v>2702663</v>
       </c>
       <c r="AO3" t="n">
-        <v>472062</v>
+        <v>377801</v>
       </c>
       <c r="AP3" t="n">
-        <v>3023527</v>
+        <v>2324862</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1019766</v>
+        <v>398528</v>
       </c>
       <c r="AR3" t="n">
-        <v>2003761</v>
+        <v>1926334</v>
       </c>
       <c r="AS3" t="n">
-        <v>1012527</v>
+        <v>774394</v>
       </c>
       <c r="AT3" t="n">
-        <v>991234</v>
+        <v>1151940</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
@@ -946,136 +938,140 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-296385.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>-5684172</v>
+        <v>-2992593</v>
       </c>
       <c r="E4" t="n">
-        <v>2981509</v>
+        <v>-740963</v>
       </c>
       <c r="F4" t="n">
-        <v>2981509</v>
+        <v>-740963</v>
       </c>
       <c r="G4" t="n">
-        <v>670714</v>
+        <v>-3058383</v>
       </c>
       <c r="H4" t="n">
-        <v>-2702663</v>
+        <v>-3733556</v>
       </c>
       <c r="I4" t="n">
-        <v>-2702663</v>
+        <v>-3733556</v>
       </c>
       <c r="J4" t="n">
-        <v>11865</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>82450</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
       <c r="L4" t="n">
-        <v>11865</v>
+        <v>82450</v>
       </c>
       <c r="M4" t="n">
-        <v>-2310795</v>
+        <v>-2613805.2</v>
       </c>
       <c r="N4" t="n">
-        <v>670714</v>
+        <v>-3058383</v>
       </c>
       <c r="O4" t="n">
-        <v>2702663</v>
+        <v>3495589</v>
       </c>
       <c r="P4" t="n">
-        <v>9972243</v>
+        <v>2967566</v>
       </c>
       <c r="Q4" t="n">
-        <v>9972243</v>
+        <v>2967566</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>670714</v>
+        <v>-3058383</v>
       </c>
       <c r="U4" t="n">
-        <v>670714</v>
+        <v>-3058383</v>
       </c>
       <c r="V4" t="n">
-        <v>670714</v>
+        <v>-3058383</v>
       </c>
       <c r="W4" t="n">
-        <v>270977</v>
+        <v>848173</v>
       </c>
       <c r="X4" t="n">
-        <v>399737</v>
+        <v>-3906556</v>
       </c>
       <c r="Y4" t="n">
-        <v>399737</v>
+        <v>-3906556</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>173000</v>
       </c>
       <c r="AA4" t="n">
-        <v>399737</v>
+        <v>-3733556</v>
       </c>
       <c r="AB4" t="n">
-        <v>3090535</v>
+        <v>-320417</v>
       </c>
       <c r="AC4" t="n">
-        <v>109026</v>
+        <v>420546</v>
       </c>
       <c r="AD4" t="n">
-        <v>1059643</v>
+        <v>-433311</v>
       </c>
       <c r="AE4" t="n">
-        <v>1401043</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-341400</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>433311</v>
       </c>
       <c r="AI4" t="n">
-        <v>1921866</v>
+        <v>-307652</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11865</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>82450</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
       <c r="AL4" t="n">
-        <v>11865</v>
+        <v>82450</v>
       </c>
       <c r="AM4" t="n">
-        <v>-2702663</v>
+        <v>-3495589</v>
       </c>
       <c r="AN4" t="n">
-        <v>2702663</v>
+        <v>3495589</v>
       </c>
       <c r="AO4" t="n">
-        <v>377801</v>
+        <v>472062</v>
       </c>
       <c r="AP4" t="n">
-        <v>2324862</v>
+        <v>3023527</v>
       </c>
       <c r="AQ4" t="n">
-        <v>398528</v>
+        <v>1019766</v>
       </c>
       <c r="AR4" t="n">
-        <v>1926334</v>
+        <v>2003761</v>
       </c>
       <c r="AS4" t="n">
-        <v>774394</v>
+        <v>1012527</v>
       </c>
       <c r="AT4" t="n">
-        <v>1151940</v>
+        <v>991234</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -1086,132 +1082,136 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-150326.687647</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.012624</v>
       </c>
       <c r="D5" t="n">
-        <v>-3543544</v>
+        <v>-1766644</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-11908245</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-11908245</v>
       </c>
       <c r="G5" t="n">
-        <v>-3142609</v>
+        <v>-7089318</v>
       </c>
       <c r="H5" t="n">
-        <v>-3543544</v>
+        <v>-13674889</v>
       </c>
       <c r="I5" t="n">
-        <v>-3543544</v>
+        <v>-13674889</v>
       </c>
       <c r="J5" t="n">
-        <v>3971</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>11479</v>
+      </c>
+      <c r="K5" t="n">
+        <v>29440</v>
+      </c>
       <c r="L5" t="n">
-        <v>3971</v>
+        <v>40919</v>
       </c>
       <c r="M5" t="n">
-        <v>-3142609</v>
+        <v>4668600.312353</v>
       </c>
       <c r="N5" t="n">
-        <v>-3142609</v>
+        <v>-7089318</v>
       </c>
       <c r="O5" t="n">
-        <v>3543544</v>
+        <v>1908481</v>
       </c>
       <c r="P5" t="n">
-        <v>7280550</v>
+        <v>3047805</v>
       </c>
       <c r="Q5" t="n">
-        <v>7280550</v>
+        <v>3047805</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.45</v>
+        <v>-2.35</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.45</v>
+        <v>-2.35</v>
       </c>
       <c r="T5" t="n">
-        <v>-3142609</v>
+        <v>-7089318</v>
       </c>
       <c r="U5" t="n">
-        <v>-3142609</v>
+        <v>-7089318</v>
       </c>
       <c r="V5" t="n">
-        <v>-3142609</v>
+        <v>-7089318</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>6442011</v>
       </c>
       <c r="X5" t="n">
-        <v>-3142609</v>
+        <v>-13531329</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3142609</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>-13531329</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-173000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>-3142609</v>
+        <v>-13704329</v>
       </c>
       <c r="AB5" t="n">
-        <v>396964</v>
+        <v>-11807327</v>
       </c>
       <c r="AC5" t="n">
-        <v>396964</v>
+        <v>100918</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+        <v>-10861288</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>10861288</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1046957</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>3971</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>11479</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>29440</v>
+      </c>
       <c r="AL5" t="n">
-        <v>3971</v>
+        <v>40919</v>
       </c>
       <c r="AM5" t="n">
-        <v>-3543544</v>
+        <v>-1908481</v>
       </c>
       <c r="AN5" t="n">
-        <v>3543544</v>
+        <v>1908481</v>
       </c>
       <c r="AO5" t="n">
-        <v>310078</v>
+        <v>436388</v>
       </c>
       <c r="AP5" t="n">
-        <v>3233466</v>
+        <v>1472093</v>
       </c>
       <c r="AQ5" t="n">
-        <v>730159</v>
+        <v>568489</v>
       </c>
       <c r="AR5" t="n">
-        <v>2503307</v>
+        <v>903604</v>
       </c>
       <c r="AS5" t="n">
-        <v>857113</v>
+        <v>700562</v>
       </c>
       <c r="AT5" t="n">
-        <v>1646194</v>
+        <v>203042</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
@@ -1463,518 +1463,518 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>15377088</v>
+        <v>9426251</v>
       </c>
       <c r="D2" t="n">
-        <v>15377088</v>
+        <v>9426251</v>
       </c>
       <c r="E2" t="n">
-        <v>14429139</v>
+        <v>12962617</v>
       </c>
       <c r="F2" t="n">
-        <v>14429139</v>
+        <v>12962617</v>
       </c>
       <c r="G2" t="n">
-        <v>1585018</v>
+        <v>2790042</v>
       </c>
       <c r="H2" t="n">
-        <v>14429139</v>
+        <v>12962617</v>
       </c>
       <c r="I2" t="n">
-        <v>14429139</v>
+        <v>12962617</v>
       </c>
       <c r="J2" t="n">
-        <v>14429139</v>
+        <v>12962617</v>
       </c>
       <c r="K2" t="n">
-        <v>14066084</v>
+        <v>12962617</v>
       </c>
       <c r="L2" t="n">
-        <v>-363055</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>14429139</v>
+        <v>12962617</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>8429009</v>
+        <v>1742753</v>
       </c>
       <c r="P2" t="n">
-        <v>-13886089</v>
+        <v>-4409102</v>
       </c>
       <c r="Q2" t="n">
-        <v>19886219</v>
+        <v>15628966</v>
       </c>
       <c r="R2" t="n">
-        <v>19886219</v>
+        <v>15628966</v>
       </c>
       <c r="S2" t="n">
-        <v>427070</v>
+        <v>4917654</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>427070</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>4917654</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4580276</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>4471250</v>
+      </c>
       <c r="Z2" t="n">
-        <v>427070</v>
+        <v>337378</v>
       </c>
       <c r="AA2" t="n">
-        <v>44500</v>
+        <v>35000</v>
       </c>
       <c r="AB2" t="n">
-        <v>382570</v>
+        <v>302378</v>
       </c>
       <c r="AC2" t="n">
-        <v>113506</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>10500</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>269064</v>
+        <v>291878</v>
       </c>
       <c r="AF2" t="n">
-        <v>14493154</v>
+        <v>17880271</v>
       </c>
       <c r="AG2" t="n">
-        <v>12481066</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>10172575</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>60950</v>
+      </c>
       <c r="AI2" t="n">
-        <v>73051</v>
+        <v>60950</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12408015</v>
+        <v>10111625</v>
       </c>
       <c r="AK2" t="n">
-        <v>2012088</v>
+        <v>7707696</v>
       </c>
       <c r="AL2" t="n">
-        <v>170576</v>
+        <v>52003</v>
       </c>
       <c r="AM2" t="n">
-        <v>498212</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>5000</v>
-      </c>
+        <v>62842</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>493212</v>
+        <v>62842</v>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>1343300</v>
+        <v>7592851</v>
       </c>
       <c r="AR2" t="n">
-        <v>1246729</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>96571</v>
+        <v>7592851</v>
       </c>
       <c r="AT2" t="n">
-        <v>96571</v>
+        <v>7592851</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>44742</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>14932114</v>
+        <v>11174001</v>
       </c>
       <c r="D3" t="n">
-        <v>14932114</v>
+        <v>11174001</v>
       </c>
       <c r="E3" t="n">
-        <v>21475445</v>
+        <v>17178806</v>
       </c>
       <c r="F3" t="n">
-        <v>21475445</v>
+        <v>17178806</v>
       </c>
       <c r="G3" t="n">
-        <v>3966963</v>
+        <v>3528929</v>
       </c>
       <c r="H3" t="n">
-        <v>21475445</v>
+        <v>17178806</v>
       </c>
       <c r="I3" t="n">
-        <v>21475445</v>
+        <v>17178806</v>
       </c>
       <c r="J3" t="n">
-        <v>21475445</v>
+        <v>17178806</v>
       </c>
       <c r="K3" t="n">
-        <v>27289370</v>
+        <v>22368485</v>
       </c>
       <c r="L3" t="n">
-        <v>5813925</v>
+        <v>5189679</v>
       </c>
       <c r="M3" t="n">
-        <v>21475445</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>17178806</v>
+      </c>
+      <c r="N3" t="n">
+        <v>214875</v>
+      </c>
       <c r="O3" t="n">
-        <v>8829497</v>
+        <v>4022689</v>
       </c>
       <c r="P3" t="n">
-        <v>-6796771</v>
+        <v>-3738388</v>
       </c>
       <c r="Q3" t="n">
-        <v>19442719</v>
+        <v>16679630</v>
       </c>
       <c r="R3" t="n">
-        <v>19442719</v>
+        <v>16679630</v>
       </c>
       <c r="S3" t="n">
-        <v>863754</v>
+        <v>2779248</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>863754</v>
-      </c>
-      <c r="V3" t="n">
-        <v>100918</v>
-      </c>
+        <v>2779248</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>173000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>173000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>589836</v>
+        <v>2779248</v>
       </c>
       <c r="AA3" t="n">
-        <v>99770</v>
+        <v>61667</v>
       </c>
       <c r="AB3" t="n">
-        <v>490066</v>
+        <v>2717581</v>
       </c>
       <c r="AC3" t="n">
-        <v>52415</v>
+        <v>671</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>883436</v>
       </c>
       <c r="AE3" t="n">
-        <v>437651</v>
+        <v>1833474</v>
       </c>
       <c r="AF3" t="n">
-        <v>28153124</v>
+        <v>25147733</v>
       </c>
       <c r="AG3" t="n">
-        <v>23322407</v>
+        <v>18839556</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
         <v>73051</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23249356</v>
+        <v>18766505</v>
       </c>
       <c r="AK3" t="n">
-        <v>4830717</v>
+        <v>6308177</v>
       </c>
       <c r="AL3" t="n">
-        <v>154856</v>
+        <v>101120</v>
       </c>
       <c r="AM3" t="n">
-        <v>104203</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>5000</v>
-      </c>
+        <v>269462</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>99203</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>104203</v>
-      </c>
+        <v>269462</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>4571658</v>
+        <v>5937595</v>
       </c>
       <c r="AR3" t="n">
-        <v>3570863</v>
+        <v>4202909</v>
       </c>
       <c r="AS3" t="n">
-        <v>1000795</v>
+        <v>1734686</v>
       </c>
       <c r="AT3" t="n">
-        <v>1000795</v>
+        <v>1734686</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45107</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>11174001</v>
+        <v>14932114</v>
       </c>
       <c r="D4" t="n">
-        <v>11174001</v>
+        <v>14932114</v>
       </c>
       <c r="E4" t="n">
-        <v>17178806</v>
+        <v>21475445</v>
       </c>
       <c r="F4" t="n">
-        <v>17178806</v>
+        <v>21475445</v>
       </c>
       <c r="G4" t="n">
-        <v>3528929</v>
+        <v>3966963</v>
       </c>
       <c r="H4" t="n">
-        <v>17178806</v>
+        <v>21475445</v>
       </c>
       <c r="I4" t="n">
-        <v>17178806</v>
+        <v>21475445</v>
       </c>
       <c r="J4" t="n">
-        <v>17178806</v>
+        <v>21475445</v>
       </c>
       <c r="K4" t="n">
-        <v>22368485</v>
+        <v>27289370</v>
       </c>
       <c r="L4" t="n">
-        <v>5189679</v>
+        <v>5813925</v>
       </c>
       <c r="M4" t="n">
-        <v>17178806</v>
-      </c>
-      <c r="N4" t="n">
-        <v>214875</v>
-      </c>
+        <v>21475445</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>4022689</v>
+        <v>8829497</v>
       </c>
       <c r="P4" t="n">
-        <v>-3738388</v>
+        <v>-6796771</v>
       </c>
       <c r="Q4" t="n">
-        <v>16679630</v>
+        <v>19442719</v>
       </c>
       <c r="R4" t="n">
-        <v>16679630</v>
+        <v>19442719</v>
       </c>
       <c r="S4" t="n">
-        <v>2779248</v>
+        <v>863754</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2779248</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>863754</v>
+      </c>
+      <c r="V4" t="n">
+        <v>100918</v>
+      </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>173000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>2779248</v>
+        <v>589836</v>
       </c>
       <c r="AA4" t="n">
-        <v>61667</v>
+        <v>99770</v>
       </c>
       <c r="AB4" t="n">
-        <v>2717581</v>
+        <v>490066</v>
       </c>
       <c r="AC4" t="n">
-        <v>671</v>
+        <v>52415</v>
       </c>
       <c r="AD4" t="n">
-        <v>883436</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1833474</v>
+        <v>437651</v>
       </c>
       <c r="AF4" t="n">
-        <v>25147733</v>
+        <v>28153124</v>
       </c>
       <c r="AG4" t="n">
-        <v>18839556</v>
+        <v>23322407</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
         <v>73051</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18766505</v>
+        <v>23249356</v>
       </c>
       <c r="AK4" t="n">
-        <v>6308177</v>
+        <v>4830717</v>
       </c>
       <c r="AL4" t="n">
-        <v>101120</v>
+        <v>154856</v>
       </c>
       <c r="AM4" t="n">
-        <v>269462</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>104203</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5000</v>
+      </c>
       <c r="AO4" t="n">
-        <v>269462</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>99203</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>104203</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>5937595</v>
+        <v>4571658</v>
       </c>
       <c r="AR4" t="n">
-        <v>4202909</v>
+        <v>3570863</v>
       </c>
       <c r="AS4" t="n">
-        <v>1734686</v>
+        <v>1000795</v>
       </c>
       <c r="AT4" t="n">
-        <v>1734686</v>
+        <v>1000795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9426251</v>
+        <v>15377088</v>
       </c>
       <c r="D5" t="n">
-        <v>9426251</v>
+        <v>15377088</v>
       </c>
       <c r="E5" t="n">
-        <v>12962617</v>
+        <v>14429139</v>
       </c>
       <c r="F5" t="n">
-        <v>12962617</v>
+        <v>14429139</v>
       </c>
       <c r="G5" t="n">
-        <v>2790042</v>
+        <v>1585018</v>
       </c>
       <c r="H5" t="n">
-        <v>12962617</v>
+        <v>14429139</v>
       </c>
       <c r="I5" t="n">
-        <v>12962617</v>
+        <v>14429139</v>
       </c>
       <c r="J5" t="n">
-        <v>12962617</v>
+        <v>14429139</v>
       </c>
       <c r="K5" t="n">
-        <v>12962617</v>
+        <v>14066084</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-363055</v>
       </c>
       <c r="M5" t="n">
-        <v>12962617</v>
+        <v>14429139</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>1742753</v>
+        <v>8429009</v>
       </c>
       <c r="P5" t="n">
-        <v>-4409102</v>
+        <v>-13886089</v>
       </c>
       <c r="Q5" t="n">
-        <v>15628966</v>
+        <v>19886219</v>
       </c>
       <c r="R5" t="n">
-        <v>15628966</v>
+        <v>19886219</v>
       </c>
       <c r="S5" t="n">
-        <v>4917654</v>
+        <v>427070</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4917654</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4580276</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
-        <v>4471250</v>
-      </c>
+        <v>427070</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>337378</v>
+        <v>427070</v>
       </c>
       <c r="AA5" t="n">
-        <v>35000</v>
+        <v>44500</v>
       </c>
       <c r="AB5" t="n">
-        <v>302378</v>
+        <v>382570</v>
       </c>
       <c r="AC5" t="n">
-        <v>10500</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>113506</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>291878</v>
+        <v>269064</v>
       </c>
       <c r="AF5" t="n">
-        <v>17880271</v>
+        <v>14493154</v>
       </c>
       <c r="AG5" t="n">
-        <v>10172575</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>60950</v>
-      </c>
+        <v>12481066</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>60950</v>
+        <v>73051</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10111625</v>
+        <v>12408015</v>
       </c>
       <c r="AK5" t="n">
-        <v>7707696</v>
+        <v>2012088</v>
       </c>
       <c r="AL5" t="n">
-        <v>52003</v>
+        <v>170576</v>
       </c>
       <c r="AM5" t="n">
-        <v>62842</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>498212</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>5000</v>
+      </c>
       <c r="AO5" t="n">
-        <v>62842</v>
+        <v>493212</v>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>7592851</v>
+        <v>1343300</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1246729</v>
       </c>
       <c r="AS5" t="n">
-        <v>7592851</v>
+        <v>96571</v>
       </c>
       <c r="AT5" t="n">
-        <v>7592851</v>
+        <v>96571</v>
       </c>
     </row>
   </sheetData>
@@ -2205,15 +2205,17 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-1525799</v>
+        <v>-2057445</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>6481964</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-96745</v>
+      </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
@@ -2221,113 +2223,113 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>96571</v>
+        <v>7592851</v>
       </c>
       <c r="H2" t="n">
-        <v>1000795</v>
+        <v>941569</v>
       </c>
       <c r="I2" t="n">
-        <v>-904224</v>
+        <v>6651282</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>12701841</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>12701841</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-240048</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6459925</v>
+      </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6481964</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>6481964</v>
       </c>
       <c r="P2" t="n">
-        <v>621575</v>
+        <v>-4089859</v>
       </c>
       <c r="Q2" t="n">
-        <v>621575</v>
+        <v>-4089859</v>
       </c>
       <c r="R2" t="n">
-        <v>-770602</v>
+        <v>-3993114</v>
       </c>
       <c r="S2" t="n">
-        <v>1277177</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1277177</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>-28950</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>-28950</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>115000</v>
+        <v>-96745</v>
       </c>
       <c r="Y2" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-96745</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1525799</v>
+        <v>-1960700</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1525799</v>
+        <v>-1960700</v>
       </c>
       <c r="AC2" t="n">
-        <v>168161</v>
+        <v>-67321</v>
       </c>
       <c r="AD2" t="n">
-        <v>101654</v>
+        <v>-23639</v>
       </c>
       <c r="AE2" t="n">
-        <v>-15720</v>
+        <v>2997</v>
       </c>
       <c r="AF2" t="n">
-        <v>82227</v>
+        <v>-46679</v>
       </c>
       <c r="AG2" t="n">
-        <v>-100918</v>
+        <v>-396964</v>
       </c>
       <c r="AH2" t="n">
-        <v>203042</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>10861288</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-173000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-173000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1046957</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1046957</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>1646194</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>-13531329</v>
+        <v>-3142609</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-2764262</v>
+        <v>-2137446</v>
       </c>
       <c r="C3" t="n">
-        <v>7419998</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-500000</v>
+        <v>-330322</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2336,127 +2338,125 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1000795</v>
+        <v>1734686</v>
       </c>
       <c r="H3" t="n">
-        <v>1734686</v>
+        <v>7592851</v>
       </c>
       <c r="I3" t="n">
-        <v>-733891</v>
+        <v>-5858165</v>
       </c>
       <c r="J3" t="n">
-        <v>7085901</v>
+        <v>1276227</v>
       </c>
       <c r="K3" t="n">
-        <v>7085901</v>
+        <v>1276227</v>
       </c>
       <c r="L3" t="n">
-        <v>-334097</v>
+        <v>116540</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1159687</v>
       </c>
       <c r="N3" t="n">
-        <v>7419998</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>7419998</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-5555530</v>
+        <v>-5327268</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5555530</v>
+        <v>-5327268</v>
       </c>
       <c r="R3" t="n">
-        <v>-5379924</v>
+        <v>-5573074</v>
       </c>
       <c r="S3" t="n">
-        <v>324394</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>324394</v>
+        <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="X3" t="n">
-        <v>-500000</v>
+        <v>45806</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>376128</v>
       </c>
       <c r="Z3" t="n">
-        <v>-500000</v>
+        <v>-330322</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2264262</v>
+        <v>-1807124</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2264262</v>
+        <v>-1807124</v>
       </c>
       <c r="AC3" t="n">
-        <v>157643</v>
+        <v>-268266</v>
       </c>
       <c r="AD3" t="n">
-        <v>46120</v>
+        <v>-12529</v>
       </c>
       <c r="AE3" t="n">
-        <v>-53736</v>
+        <v>-49117</v>
       </c>
       <c r="AF3" t="n">
-        <v>165259</v>
+        <v>-206620</v>
       </c>
       <c r="AG3" t="n">
-        <v>-420546</v>
+        <v>-109026</v>
       </c>
       <c r="AH3" t="n">
-        <v>991234</v>
+        <v>1151940</v>
       </c>
       <c r="AI3" t="n">
-        <v>307652</v>
+        <v>-1921866</v>
       </c>
       <c r="AJ3" t="n">
-        <v>433311</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>173000</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>173000</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>307652</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>307652</v>
-      </c>
+        <v>-1059643</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>-1401043</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>341400</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-3906556</v>
+        <v>399737</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-2137446</v>
+        <v>-2764262</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>7419998</v>
       </c>
       <c r="D4" t="n">
-        <v>-330322</v>
+        <v>-500000</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2465,126 +2465,126 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>1000795</v>
+      </c>
+      <c r="H4" t="n">
         <v>1734686</v>
       </c>
-      <c r="H4" t="n">
-        <v>7592851</v>
-      </c>
       <c r="I4" t="n">
-        <v>-5858165</v>
+        <v>-733891</v>
       </c>
       <c r="J4" t="n">
-        <v>1276227</v>
+        <v>7085901</v>
       </c>
       <c r="K4" t="n">
-        <v>1276227</v>
+        <v>7085901</v>
       </c>
       <c r="L4" t="n">
-        <v>116540</v>
+        <v>-334097</v>
       </c>
       <c r="M4" t="n">
-        <v>1159687</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7419998</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>7419998</v>
       </c>
       <c r="P4" t="n">
-        <v>-5327268</v>
+        <v>-5555530</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5327268</v>
+        <v>-5555530</v>
       </c>
       <c r="R4" t="n">
-        <v>-5573074</v>
+        <v>-5379924</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>324394</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>324394</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45806</v>
+        <v>-500000</v>
       </c>
       <c r="Y4" t="n">
-        <v>376128</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-330322</v>
+        <v>-500000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1807124</v>
+        <v>-2264262</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1807124</v>
+        <v>-2264262</v>
       </c>
       <c r="AC4" t="n">
-        <v>-268266</v>
+        <v>157643</v>
       </c>
       <c r="AD4" t="n">
-        <v>-12529</v>
+        <v>46120</v>
       </c>
       <c r="AE4" t="n">
-        <v>-49117</v>
+        <v>-53736</v>
       </c>
       <c r="AF4" t="n">
-        <v>-206620</v>
+        <v>165259</v>
       </c>
       <c r="AG4" t="n">
-        <v>-109026</v>
+        <v>-420546</v>
       </c>
       <c r="AH4" t="n">
-        <v>1151940</v>
+        <v>991234</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1921866</v>
+        <v>307652</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>433311</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>173000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>173000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1059643</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>307652</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>307652</v>
+      </c>
       <c r="AO4" t="n">
-        <v>-1401043</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>341400</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>399737</v>
+        <v>-3906556</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-2057445</v>
+        <v>-1525799</v>
       </c>
       <c r="C5" t="n">
-        <v>6481964</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-96745</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>0</v>
       </c>
@@ -2592,99 +2592,99 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>7592851</v>
+        <v>96571</v>
       </c>
       <c r="H5" t="n">
-        <v>941569</v>
+        <v>1000795</v>
       </c>
       <c r="I5" t="n">
-        <v>6651282</v>
+        <v>-904224</v>
       </c>
       <c r="J5" t="n">
-        <v>12701841</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12701841</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-240048</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6459925</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>6481964</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6481964</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-4089859</v>
+        <v>621575</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4089859</v>
+        <v>621575</v>
       </c>
       <c r="R5" t="n">
-        <v>-3993114</v>
+        <v>-770602</v>
       </c>
       <c r="S5" t="n">
-        <v>-28950</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>-28950</v>
-      </c>
+        <v>1277177</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1277177</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-96745</v>
+        <v>115000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-96745</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1960700</v>
+        <v>-1525799</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1960700</v>
+        <v>-1525799</v>
       </c>
       <c r="AC5" t="n">
-        <v>-67321</v>
+        <v>168161</v>
       </c>
       <c r="AD5" t="n">
-        <v>-23639</v>
+        <v>101654</v>
       </c>
       <c r="AE5" t="n">
-        <v>2997</v>
+        <v>-15720</v>
       </c>
       <c r="AF5" t="n">
-        <v>-46679</v>
+        <v>82227</v>
       </c>
       <c r="AG5" t="n">
-        <v>-396964</v>
+        <v>-100918</v>
       </c>
       <c r="AH5" t="n">
-        <v>1646194</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
+        <v>203042</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>10861288</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-173000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-173000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1046957</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1046957</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>-3142609</v>
+        <v>-13531329</v>
       </c>
     </row>
   </sheetData>
@@ -3169,187 +3169,187 @@
       </c>
       <c r="CP1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EA1" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Mark  Scott', 'age': 46, 'title': 'President, CEO &amp; Director', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 223992, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Michael  Adams', 'title': 'Managing Director of Star Finance GmbH', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Mark  Scott', 'age': 46, 'title': 'President, CEO &amp; Director', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 221555, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Michael  Adams', 'title': 'Managing Director of Star Finance GmbH', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.419</v>
+        <v>1.227</v>
       </c>
       <c r="AF2" t="n">
         <v>38000</v>
@@ -3516,7 +3516,7 @@
         <v>411852</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.008</v>
+        <v>0.0115</v>
       </c>
       <c r="AP2" t="n">
         <v>0.0365</v>
@@ -3531,7 +3531,7 @@
         <v>0.0155</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0161225</v>
+        <v>0.0162625</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -3569,10 +3569,10 @@
         <v>16637088</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.50771624</v>
+        <v>0.5021242</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.030528864</v>
+        <v>0.030868856</v>
       </c>
       <c r="BH2" t="n">
         <v>1719705600</v>
@@ -3604,7 +3604,7 @@
         <v>-0.03125</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -3698,138 +3698,138 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CR2" t="n">
+        <v>1762239644</v>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>finmb_625819883</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="CY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1605078000000</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>0.0155 - 0.0155</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.0039999997</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.34782606</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.0115 - 0.0365</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.5753425</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-3.125</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1747771200</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1747771200</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.00076249987</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.046887003</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>Sassy Gold Corp.</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
           <t>Sassy Gold Corp.              R</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>Sassy Gold Corp.</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CS2" t="n">
-        <v>1762239644</v>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>finmb_625819883</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="CX2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="CZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="n">
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>0.0155</v>
-      </c>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>1605078000000</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>0.0155 - 0.0155</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.0074999994</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.9374999000000001</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>0.008 - 0.0365</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.5753425</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-3.125</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>1747771200</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1747771200</v>
-      </c>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.00062249973</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.038610622</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
       </c>
       <c r="EA2" t="inlineStr"/>
     </row>
